--- a/docs/phase-2a/01a_Project_Plan_Workbook.xlsx
+++ b/docs/phase-2a/01a_Project_Plan_Workbook.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource loading" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule'!$A$3:$I$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule'!$A$3:$I$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A3AA7"/>
+        <fgColor rgb="002A78D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002A78D6"/>
+        <fgColor rgb="004A3AA7"/>
       </patternFill>
     </fill>
     <fill>
@@ -226,7 +226,7 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB80"/>
+  <dimension ref="A1:BB84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Release R1 — Public Launch + F1, F2 (20 Oct 2026)</t>
+          <t>Release R1 — Public Launch + F3 Shared Identity (20 Oct 2026)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>AI-assisted Phase 1 assessment: codebase map, ERD, API inventory, dependency &amp; security scan, defect triage</t>
+          <t>AI-assisted Phase 1 assessment: codebase map, ERD, API inventory, auth/user tables, dependency &amp; security scan, defect triage</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Launch Scope Gate: launch scope, go-live criteria, F1/F2 confirmed</t>
+          <t>Launch Scope Gate: launch scope, go-live criteria, F3 scope and fallback confirmed</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Security baseline: SAST, dependency &amp; DAST scans; VAPT of launch surface</t>
+          <t>F3 — Identity design &amp; ADR-01: linking rules, identifiers, role model, KYC fields, token design</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1576,30 +1576,29 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>46308</v>
+        <v>46297</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1SS,D22</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Release 2A.0 launch</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
+          <t>Foundation &amp; identity</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1609,7 +1608,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Performance / load test at SportSeek-defined launch concurrency</t>
+          <t>F3 — Identity service in .NET (OIDC client per app; one credential &amp; profile; multi-role; KYC status on identity)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1623,26 +1622,26 @@
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>46308</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>2.3SS,D5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Release 2A.0 launch</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
+          <t>Foundation &amp; identity</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="n"/>
+      <c r="L18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1652,7 +1651,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Store &amp; compliance readiness: listings, privacy policy, DPDP notice/consent, account deletion</t>
+          <t>F3 — OTP-verified account linking and role assignment in User &amp; Partner app registration (React Native) + Admin role view</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1669,23 +1668,23 @@
         <v>46300</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2.2,D6</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Release 2A.0 launch</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
+          <t>Foundation &amp; identity</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1695,7 +1694,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>F1 — Email notifications for all live alert triggers (booking, registration, payment)</t>
+          <t>F3 — Bootstrap: load all existing User &amp; Partner accounts 1:1 into the identity store (duplicates merged in R2)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -1705,30 +1704,30 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>2.2,D14</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Release 2A.0 launch</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
+          <t>Foundation &amp; identity</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1738,7 +1737,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>F2 — Booking &amp; event reminders (T-24h, T-2h) by Email/SMS</t>
+          <t>F3 — Remote feature flag with fallback to Phase 1 login; minimum-version enforcement</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1752,72 +1751,69 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Foundation &amp; identity</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="n"/>
+      <c r="L21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Security baseline: SAST, dependency &amp; DAST; VAPT of launch surface + targeted identity pen test</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
         <v>46300</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>2.2,D12</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="F22" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Release 2A.0 launch</t>
         </is>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>Code freeze &amp; Release Candidate</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Srivin</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>46309</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>2.5,2.9,2.10</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>Release 2A.0 launch</t>
-        </is>
-      </c>
-      <c r="L22" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="K22" s="16" t="n"/>
+      <c r="L22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1827,7 +1823,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>App store submissions &amp; review window</t>
+          <t>Performance / load test at launch concurrency, incl. login and OTP flows</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1837,21 +1833,21 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Joint</t>
+          <t>Srivin</t>
         </is>
       </c>
       <c r="E23" s="10" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F23" s="10" t="n">
         <v>46309</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>46314</v>
-      </c>
       <c r="G23" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2.11,2.8</t>
+          <t>2.3SS,D5</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -1859,8 +1855,8 @@
           <t>Release 2A.0 launch</t>
         </is>
       </c>
+      <c r="K23" s="16" t="n"/>
       <c r="L23" s="16" t="n"/>
-      <c r="M23" s="16" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1870,7 +1866,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Full regression + VAPT retest + UAT by SportSeek testers</t>
+          <t>Store &amp; compliance readiness: listings, privacy policy, DPDP notice/consent, account deletion</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -1884,160 +1880,158 @@
         </is>
       </c>
       <c r="E24" s="10" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>2.2,D6</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Release 2A.0 launch</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="n"/>
+      <c r="L24" s="16" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Code freeze &amp; Release Candidate (F3 behind flag)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>2.5,2.7,2.8,2.9,2.10</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Release 2A.0 launch</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>App store submissions &amp; review window</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>46314</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>2.14,2.13</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Release 2A.0 launch</t>
+        </is>
+      </c>
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Full regression + identity/VAPT retest + UAT incl. account-linking scenarios</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>46310</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F27" s="10" t="n">
         <v>46314</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G27" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Release 2A.0 launch</t>
         </is>
       </c>
-      <c r="L24" s="16" t="n"/>
-      <c r="M24" s="16" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Launch runbook, rollback plan, on-call rota, war-room</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Srivin</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>Release 2A.0 launch</t>
-        </is>
-      </c>
-      <c r="L25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Go / No-Go</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>SportSeek</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>46314</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>2.12,2.13,2.14</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>Release 2A.0 launch</t>
-        </is>
-      </c>
-      <c r="M26" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>R1 LIVE — public launch with F1 and F2</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>46315</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>Release 2A.0 launch</t>
-        </is>
-      </c>
-      <c r="M27" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="L27" s="16" t="n"/>
+      <c r="M27" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -2047,7 +2041,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Hypercare (daily triage, extended monitoring)</t>
+          <t>Launch runbook, rollback plan (incl. F3 switch-off), on-call rota, war-room</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -2061,133 +2055,127 @@
         </is>
       </c>
       <c r="E28" s="10" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Release 2A.0 launch</t>
+        </is>
+      </c>
+      <c r="L28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Go / No-Go (separate decision: F3 on or off at launch)</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>SportSeek</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>46314</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>2.15,2.16,2.17</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Release 2A.0 launch</t>
+        </is>
+      </c>
+      <c r="M29" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>R1 LIVE — public launch with F3 Shared Identity</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n">
         <v>46315</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="F30" s="14" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>Release 2A.0 launch</t>
         </is>
       </c>
-      <c r="M28" s="16" t="n"/>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Discovery, Architecture &amp; Design (AI-assisted, runs alongside launch)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>46444</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Discovery &amp; design</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
-      <c r="P29" s="7" t="n"/>
-      <c r="Q29" s="7" t="n"/>
-      <c r="R29" s="7" t="n"/>
-      <c r="S29" s="7" t="n"/>
-      <c r="T29" s="7" t="n"/>
-      <c r="U29" s="7" t="n"/>
-      <c r="V29" s="7" t="n"/>
-      <c r="W29" s="7" t="n"/>
-      <c r="X29" s="7" t="n"/>
-      <c r="Y29" s="7" t="n"/>
-      <c r="Z29" s="7" t="n"/>
-      <c r="AA29" s="7" t="n"/>
-      <c r="AB29" s="7" t="n"/>
-      <c r="AC29" s="7" t="n"/>
-      <c r="AD29" s="7" t="n"/>
-      <c r="AE29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>AI-generated as-is documentation: architecture, ERD, API catalogue, integration map</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Srivin</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>46304</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>Discovery &amp; design</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="n"/>
+      <c r="M30" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Story mapping for F3–F12; AI-drafted stories &amp; acceptance criteria refined with PO</t>
+          <t>Hypercare (daily triage, identity and login monitoring)</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -2197,129 +2185,137 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Joint</t>
+          <t>Srivin</t>
         </is>
       </c>
       <c r="E31" s="10" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>46332</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>Release 2A.0 launch</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="n"/>
+      <c r="N31" s="16" t="n"/>
+      <c r="O31" s="16" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Discovery, Architecture &amp; Design (AI-assisted, runs alongside launch)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="6" t="n">
         <v>46300</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>3.1SS,D8</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="F32" s="6" t="n">
+        <v>46444</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Discovery &amp; design</t>
         </is>
       </c>
-      <c r="K31" s="17" t="n"/>
-      <c r="L31" s="17" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>HLD &amp; ADRs (identity, event bus, service-type model, web framework)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="7" t="n"/>
+      <c r="O32" s="7" t="n"/>
+      <c r="P32" s="7" t="n"/>
+      <c r="Q32" s="7" t="n"/>
+      <c r="R32" s="7" t="n"/>
+      <c r="S32" s="7" t="n"/>
+      <c r="T32" s="7" t="n"/>
+      <c r="U32" s="7" t="n"/>
+      <c r="V32" s="7" t="n"/>
+      <c r="W32" s="7" t="n"/>
+      <c r="X32" s="7" t="n"/>
+      <c r="Y32" s="7" t="n"/>
+      <c r="Z32" s="7" t="n"/>
+      <c r="AA32" s="7" t="n"/>
+      <c r="AB32" s="7" t="n"/>
+      <c r="AC32" s="7" t="n"/>
+      <c r="AD32" s="7" t="n"/>
+      <c r="AE32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>AI-generated as-is documentation: architecture, ERD, API catalogue, integration map</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Srivin</t>
         </is>
       </c>
-      <c r="E32" s="10" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>46318</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="E33" s="10" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Discovery &amp; design</t>
         </is>
       </c>
-      <c r="L32" s="17" t="n"/>
-      <c r="M32" s="17" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>HLD sign-off</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>SportSeek</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>46318</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>Discovery &amp; design</t>
-        </is>
-      </c>
-      <c r="M33" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="K33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Design system (atomic) with AI-assisted exploration; tokens shared by mobile &amp; web</t>
+          <t>Story mapping for F1, F2, F4–F12; AI-drafted stories &amp; acceptance criteria refined with PO</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -2329,147 +2325,129 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E34" s="10" t="n">
         <v>46300</v>
       </c>
       <c r="F34" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>3.1SS,D8</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Discovery &amp; design</t>
+        </is>
+      </c>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>HLD &amp; remaining ADRs (event bus, service-type model, web framework); identity ADR-01 taken in R1</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F35" s="10" t="n">
         <v>46318</v>
       </c>
-      <c r="G34" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>3.2SS</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="G35" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>Discovery &amp; design</t>
         </is>
       </c>
-      <c r="K34" s="17" t="n"/>
-      <c r="L34" s="17" t="n"/>
-      <c r="M34" s="17" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>Design system approval</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>HLD sign-off</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>SportSeek</t>
         </is>
       </c>
-      <c r="E35" s="14" t="n">
+      <c r="E36" s="14" t="n">
         <v>46318</v>
       </c>
-      <c r="F35" s="14" t="n">
+      <c r="F36" s="14" t="n">
         <v>46318</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>Discovery &amp; design</t>
         </is>
       </c>
-      <c r="M35" s="15" t="inlineStr">
+      <c r="M36" s="15" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Feature specs, UI and LLD — produced one train ahead of build (spec-driven development)</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>46444</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>3.3SS</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Discovery &amp; design</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="n"/>
-      <c r="N36" s="17" t="n"/>
-      <c r="O36" s="17" t="n"/>
-      <c r="P36" s="17" t="n"/>
-      <c r="Q36" s="17" t="n"/>
-      <c r="R36" s="17" t="n"/>
-      <c r="S36" s="17" t="n"/>
-      <c r="T36" s="17" t="n"/>
-      <c r="U36" s="17" t="n"/>
-      <c r="V36" s="17" t="n"/>
-      <c r="W36" s="17" t="n"/>
-      <c r="X36" s="17" t="n"/>
-      <c r="Y36" s="17" t="n"/>
-      <c r="Z36" s="17" t="n"/>
-      <c r="AA36" s="17" t="n"/>
-      <c r="AB36" s="17" t="n"/>
-      <c r="AC36" s="17" t="n"/>
-      <c r="AD36" s="17" t="n"/>
-      <c r="AE36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Closure of SOW open items (ledger visibility, alert catalog, SLAs, NFRs, refund policy, Route)</t>
+          <t>Design system (atomic) with AI-assisted exploration; tokens shared by mobile &amp; web</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -2479,21 +2457,21 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>SportSeek</t>
+          <t>Srivin</t>
         </is>
       </c>
       <c r="E37" s="10" t="n">
         <v>46300</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>46395</v>
+        <v>46318</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>D10,D11,D15,D16,D20</t>
+          <t>3.2SS</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -2501,66 +2479,65 @@
           <t>Discovery &amp; design</t>
         </is>
       </c>
-      <c r="K37" s="17" t="n"/>
-      <c r="L37" s="17" t="n"/>
-      <c r="M37" s="17" t="n"/>
-      <c r="N37" s="17" t="n"/>
-      <c r="O37" s="17" t="n"/>
-      <c r="P37" s="17" t="n"/>
-      <c r="Q37" s="17" t="n"/>
-      <c r="R37" s="17" t="n"/>
-      <c r="S37" s="17" t="n"/>
-      <c r="T37" s="17" t="n"/>
-      <c r="U37" s="17" t="n"/>
-      <c r="V37" s="17" t="n"/>
-      <c r="W37" s="17" t="n"/>
-      <c r="X37" s="17" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="18" t="n"/>
+      <c r="M37" s="18" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Platform Foundation (M1) — built in the first build cycle</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="6" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Foundation &amp; identity</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="n"/>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="7" t="n"/>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Design system approval</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>SportSeek</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>46318</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>Discovery &amp; design</t>
+        </is>
+      </c>
+      <c r="M38" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code; Dev / Staging / Prod promotion</t>
+          <t>Feature specs, UI and LLD — produced one train ahead of build (spec-driven development)</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -2570,17 +2547,17 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E39" s="10" t="n">
         <v>46314</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>46325</v>
+        <v>46444</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
@@ -2589,21 +2566,38 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Foundation &amp; identity</t>
+          <t>Discovery &amp; design</t>
         </is>
       </c>
       <c r="M39" s="18" t="n"/>
       <c r="N39" s="18" t="n"/>
+      <c r="O39" s="18" t="n"/>
+      <c r="P39" s="18" t="n"/>
+      <c r="Q39" s="18" t="n"/>
+      <c r="R39" s="18" t="n"/>
+      <c r="S39" s="18" t="n"/>
+      <c r="T39" s="18" t="n"/>
+      <c r="U39" s="18" t="n"/>
+      <c r="V39" s="18" t="n"/>
+      <c r="W39" s="18" t="n"/>
+      <c r="X39" s="18" t="n"/>
+      <c r="Y39" s="18" t="n"/>
+      <c r="Z39" s="18" t="n"/>
+      <c r="AA39" s="18" t="n"/>
+      <c r="AB39" s="18" t="n"/>
+      <c r="AC39" s="18" t="n"/>
+      <c r="AD39" s="18" t="n"/>
+      <c r="AE39" s="18" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>CI/CD quality gates incl. AI code review, SAST, dependency &amp; secret scanning, coverage</t>
+          <t>Closure of SOW open items (ledger visibility, alert catalog, SLAs, NFRs, refund policy, Route)</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -2613,168 +2607,174 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>SportSeek</t>
         </is>
       </c>
       <c r="E40" s="10" t="n">
-        <v>46314</v>
+        <v>46300</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>46325</v>
+        <v>46395</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>3.3SS</t>
+          <t>D10,D11,D15,D16,D20</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Foundation &amp; identity</t>
-        </is>
-      </c>
+          <t>Discovery &amp; design</t>
+        </is>
+      </c>
+      <c r="K40" s="18" t="n"/>
+      <c r="L40" s="18" t="n"/>
       <c r="M40" s="18" t="n"/>
       <c r="N40" s="18" t="n"/>
+      <c r="O40" s="18" t="n"/>
+      <c r="P40" s="18" t="n"/>
+      <c r="Q40" s="18" t="n"/>
+      <c r="R40" s="18" t="n"/>
+      <c r="S40" s="18" t="n"/>
+      <c r="T40" s="18" t="n"/>
+      <c r="U40" s="18" t="n"/>
+      <c r="V40" s="18" t="n"/>
+      <c r="W40" s="18" t="n"/>
+      <c r="X40" s="18" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Event bus (transactional outbox), API Gateway/BFF, feature-flag service</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Platform Foundation (M1) — built in the first build cycle</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>46332</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Foundation &amp; identity</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="7" t="n"/>
+      <c r="O41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Infrastructure-as-Code; Dev / Staging / Prod promotion</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Srivin</t>
         </is>
       </c>
-      <c r="E41" s="10" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G41" s="8" t="n">
+      <c r="E42" s="10" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>46325</v>
+      </c>
+      <c r="G42" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>3.3SS</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Foundation &amp; identity</t>
         </is>
       </c>
-      <c r="N41" s="18" t="n"/>
-      <c r="O41" s="18" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>M1 Foundation accepted</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>SportSeek</t>
-        </is>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>46332</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>4.1,4.2,4.3</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="M42" s="17" t="n"/>
+      <c r="N42" s="17" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>CI/CD quality gates incl. AI code review, SAST, dependency &amp; secret scanning, coverage</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>46325</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>3.3SS</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Foundation &amp; identity</t>
         </is>
       </c>
-      <c r="O42" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Release R2 — F3 Shared Identity, F4 Push &amp; Preferences (24 Nov 2026)</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="6" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Foundation &amp; identity</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="n"/>
-      <c r="O43" s="7" t="n"/>
-      <c r="P43" s="7" t="n"/>
-      <c r="Q43" s="7" t="n"/>
-      <c r="R43" s="7" t="n"/>
-      <c r="S43" s="7" t="n"/>
+      <c r="M43" s="17" t="n"/>
+      <c r="N43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>F3 — Shared identity: OIDC clients per app, OTP-verified account linking, multi-role, KYC reuse</t>
+          <t>Event bus (transactional outbox), API Gateway/BFF, feature-flag service</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -2784,21 +2784,21 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Joint</t>
+          <t>Srivin</t>
         </is>
       </c>
       <c r="E44" s="10" t="n">
         <v>46321</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>3.4,3.6</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -2806,151 +2806,146 @@
           <t>Foundation &amp; identity</t>
         </is>
       </c>
-      <c r="N44" s="18" t="n"/>
-      <c r="O44" s="18" t="n"/>
-      <c r="P44" s="18" t="n"/>
+      <c r="N44" s="17" t="n"/>
+      <c r="O44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>F4 — Push notifications (FCM/APNs) + role-scoped notification preferences</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>M1 Foundation accepted</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>SportSeek</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>46332</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>46332</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>4.1,4.2,4.3</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>Foundation &amp; identity</t>
+        </is>
+      </c>
+      <c r="O45" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Release R2 — F1 Email, F2 Reminders, F4 Push &amp; Preferences (24 Nov 2026)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="6" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+      <c r="P46" s="7" t="n"/>
+      <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="7" t="n"/>
+      <c r="S46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>F1 — Email notifications for all live alert triggers (booking, registration, payment)</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Srivin</t>
         </is>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E47" s="10" t="n">
         <v>46321</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="G45" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="F47" s="10" t="n">
+        <v>46332</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>3.4,D14</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="N45" s="19" t="n"/>
-      <c r="O45" s="19" t="n"/>
-      <c r="P45" s="19" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>Hardening: regression, targeted pen test on identity, UAT; store submission</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>46342</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>46346</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>5.1,5.2</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="Q46" s="11" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>R2 LIVE — F3, F4</t>
-        </is>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>46350</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>46350</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="R47" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="N47" s="19" t="n"/>
+      <c r="O47" s="19" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Hypercare + KT checklist sign-off (R2)</t>
+          <t>F2 — Booking &amp; event reminders (T-24h, T-2h) by Email/SMS/Push</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -2964,75 +2959,80 @@
         </is>
       </c>
       <c r="E48" s="10" t="n">
-        <v>46350</v>
+        <v>46328</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>46356</v>
+        <v>46339</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.1SS,D12</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="R48" s="11" t="n"/>
-      <c r="S48" s="11" t="n"/>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="O48" s="19" t="n"/>
+      <c r="P48" s="19" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Release R3 — F5 Cancellation &amp; Refunds, F6 Web App (Players) (22 Dec 2026)</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="6" t="n">
-        <v>46351</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>46385</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>Booking &amp; events</t>
-        </is>
-      </c>
-      <c r="R49" s="7" t="n"/>
-      <c r="S49" s="7" t="n"/>
-      <c r="T49" s="7" t="n"/>
-      <c r="U49" s="7" t="n"/>
-      <c r="V49" s="7" t="n"/>
-      <c r="W49" s="7" t="n"/>
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>F4 — Push notifications (FCM/APNs) + role-scoped notification preferences + cross-app deep links</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>3.4,D14</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="N49" s="19" t="n"/>
+      <c r="O49" s="19" t="n"/>
+      <c r="P49" s="19" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>F5 — Cancellation &amp; refunds for bookings and tournament registrations (gateway refund API, policy rules)</t>
+          <t>Enabler — reconciliation &amp; merge of existing duplicate accounts (approved merge rules)</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -3042,41 +3042,41 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E50" s="10" t="n">
-        <v>46351</v>
+        <v>46321</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>46367</v>
+        <v>46339</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>5.4,D11</t>
+          <t>2.19,D18</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Booking &amp; events</t>
-        </is>
-      </c>
-      <c r="R50" s="20" t="n"/>
-      <c r="S50" s="20" t="n"/>
-      <c r="T50" s="20" t="n"/>
+          <t>Foundation &amp; identity</t>
+        </is>
+      </c>
+      <c r="N50" s="17" t="n"/>
+      <c r="O50" s="17" t="n"/>
+      <c r="P50" s="17" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>F6 — Web app for players: search, availability, booking, event registration, payments</t>
+          <t>Hardening: regression, identity-merge dry-run sign-off, UAT; store submission</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -3086,85 +3086,85 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E51" s="10" t="n">
-        <v>46351</v>
+        <v>46342</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>46367</v>
+        <v>46346</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>5.4,3.6</t>
+          <t>5.1,5.2,5.3,5.4</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Web application</t>
-        </is>
-      </c>
-      <c r="R51" s="21" t="n"/>
-      <c r="S51" s="21" t="n"/>
-      <c r="T51" s="21" t="n"/>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="Q51" s="11" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Enabler — reconciliation &amp; migration of existing duplicate accounts</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>R2 LIVE — F1, F2, F4; duplicate accounts merged</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>Joint</t>
         </is>
       </c>
-      <c r="E52" s="10" t="n">
-        <v>46351</v>
-      </c>
-      <c r="F52" s="10" t="n">
-        <v>46367</v>
-      </c>
-      <c r="G52" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>5.4,D18</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>Foundation &amp; identity</t>
-        </is>
-      </c>
-      <c r="R52" s="18" t="n"/>
-      <c r="S52" s="18" t="n"/>
-      <c r="T52" s="18" t="n"/>
+      <c r="E52" s="14" t="n">
+        <v>46350</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>46350</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="R52" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Hardening: regression, targeted pen test on refunds, UAT; store submission</t>
+          <t>Hypercare + KT checklist sign-off (R2)</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -3174,21 +3174,21 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Joint</t>
+          <t>Srivin</t>
         </is>
       </c>
       <c r="E53" s="10" t="n">
-        <v>46370</v>
+        <v>46350</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>46374</v>
+        <v>46356</v>
       </c>
       <c r="G53" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>6.1,6.2,6.3</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
@@ -3196,63 +3196,57 @@
           <t>Release, KT &amp; warranty</t>
         </is>
       </c>
-      <c r="U53" s="11" t="n"/>
+      <c r="R53" s="11" t="n"/>
+      <c r="S53" s="11" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>R3 LIVE — F5, F6</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>46378</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>46378</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="V54" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Release R3 — F5 Cancellation &amp; Refunds, F6 Web App (Players) (22 Dec 2026)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="6" t="n">
+        <v>46351</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>46385</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Booking &amp; events</t>
+        </is>
+      </c>
+      <c r="R54" s="7" t="n"/>
+      <c r="S54" s="7" t="n"/>
+      <c r="T54" s="7" t="n"/>
+      <c r="U54" s="7" t="n"/>
+      <c r="V54" s="7" t="n"/>
+      <c r="W54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Hypercare + KT checklist sign-off (R3)</t>
+          <t>F5 — Cancellation &amp; refunds for bookings and tournament registrations (gateway refund API, policy rules)</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -3266,76 +3260,81 @@
         </is>
       </c>
       <c r="E55" s="10" t="n">
-        <v>46378</v>
+        <v>46351</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>46385</v>
+        <v>46367</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.6,D11</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="V55" s="11" t="n"/>
-      <c r="W55" s="11" t="n"/>
+          <t>Booking &amp; events</t>
+        </is>
+      </c>
+      <c r="R55" s="20" t="n"/>
+      <c r="S55" s="20" t="n"/>
+      <c r="T55" s="20" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Release R4 — F7 Generalised Partner Model, F8 Waitlist &amp; Edit Alerts (27 Jan 2027)</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="6" t="n">
-        <v>46379</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>46420</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" s="4" t="inlineStr"/>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>Partner &amp; service</t>
-        </is>
-      </c>
-      <c r="V56" s="7" t="n"/>
-      <c r="W56" s="7" t="n"/>
-      <c r="X56" s="7" t="n"/>
-      <c r="Y56" s="7" t="n"/>
-      <c r="Z56" s="7" t="n"/>
-      <c r="AA56" s="7" t="n"/>
-      <c r="AB56" s="7" t="n"/>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>F6 — Web app for players: search, availability, booking, event registration, payments</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>46351</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>46367</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>5.6,3.6</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>Web application</t>
+        </is>
+      </c>
+      <c r="R56" s="21" t="n"/>
+      <c r="S56" s="21" t="n"/>
+      <c r="T56" s="21" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>F7 — Generalised partner/service model; coach, physio, nutritionist enabled by admin configuration</t>
+          <t>Hardening: regression, targeted pen test on refunds, UAT; store submission</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -3345,87 +3344,85 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E57" s="10" t="n">
-        <v>46379</v>
+        <v>46370</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>46402</v>
+        <v>46374</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.1,6.2</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Partner &amp; service</t>
-        </is>
-      </c>
-      <c r="V57" s="22" t="n"/>
-      <c r="W57" s="22" t="n"/>
-      <c r="X57" s="22" t="n"/>
-      <c r="Y57" s="22" t="n"/>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="U57" s="11" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>F8 — Waitlist with time-boxed offers + event-edited-after-publish notifications</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Srivin</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>46379</v>
-      </c>
-      <c r="F58" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="G58" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>Booking &amp; events</t>
-        </is>
-      </c>
-      <c r="V58" s="20" t="n"/>
-      <c r="W58" s="20" t="n"/>
-      <c r="X58" s="20" t="n"/>
-      <c r="Y58" s="20" t="n"/>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>R3 LIVE — F5, F6</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v>46378</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>46378</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="V58" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Hardening: facility regression, UAT; store submission (reduced capacity over year-end)</t>
+          <t>Hypercare + KT checklist sign-off (R3)</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -3435,21 +3432,21 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Joint</t>
+          <t>Srivin</t>
         </is>
       </c>
       <c r="E59" s="10" t="n">
-        <v>46405</v>
+        <v>46378</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>46409</v>
+        <v>46385</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>7.1,7.2</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
@@ -3457,63 +3454,58 @@
           <t>Release, KT &amp; warranty</t>
         </is>
       </c>
-      <c r="Z59" s="11" t="n"/>
+      <c r="V59" s="11" t="n"/>
+      <c r="W59" s="11" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>R4 LIVE — F7, F8</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>46414</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>46414</v>
-      </c>
-      <c r="G60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="12" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="I60" s="12" t="inlineStr">
-        <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="AA60" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Release R4 — F7 Generalised Partner Model, F8 Waitlist &amp; Edit Alerts (27 Jan 2027)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="6" t="n">
+        <v>46379</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>46420</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Partner &amp; service</t>
+        </is>
+      </c>
+      <c r="V60" s="7" t="n"/>
+      <c r="W60" s="7" t="n"/>
+      <c r="X60" s="7" t="n"/>
+      <c r="Y60" s="7" t="n"/>
+      <c r="Z60" s="7" t="n"/>
+      <c r="AA60" s="7" t="n"/>
+      <c r="AB60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Hypercare + KT checklist sign-off (R4)</t>
+          <t>F7 — Generalised partner/service model; coach, physio, nutritionist enabled by admin configuration</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -3527,75 +3519,83 @@
         </is>
       </c>
       <c r="E61" s="10" t="n">
-        <v>46414</v>
+        <v>46379</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>46420</v>
+        <v>46402</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="AA61" s="11" t="n"/>
-      <c r="AB61" s="11" t="n"/>
+          <t>Partner &amp; service</t>
+        </is>
+      </c>
+      <c r="V61" s="22" t="n"/>
+      <c r="W61" s="22" t="n"/>
+      <c r="X61" s="22" t="n"/>
+      <c r="Y61" s="22" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Release R5 — F9 Transaction Ledger, F10 Web App (Organisers &amp; Partners) (23 Feb 2027)</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="6" t="n">
-        <v>46415</v>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>46448</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H62" s="4" t="inlineStr"/>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>Transaction ledger</t>
-        </is>
-      </c>
-      <c r="AA62" s="7" t="n"/>
-      <c r="AB62" s="7" t="n"/>
-      <c r="AC62" s="7" t="n"/>
-      <c r="AD62" s="7" t="n"/>
-      <c r="AE62" s="7" t="n"/>
-      <c r="AF62" s="7" t="n"/>
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>F8 — Waitlist with time-boxed offers + event-edited-after-publish notifications</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>46379</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>Booking &amp; events</t>
+        </is>
+      </c>
+      <c r="V62" s="20" t="n"/>
+      <c r="W62" s="20" t="n"/>
+      <c r="X62" s="20" t="n"/>
+      <c r="Y62" s="20" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>F9 — Transaction Ledger: webhook ingestion + reconciliation, admin history/detail, PDF/CSV export, refund tracker</t>
+          <t>Hardening: facility regression, UAT; store submission (reduced capacity over year-end)</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -3605,85 +3605,85 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E63" s="10" t="n">
-        <v>46415</v>
+        <v>46405</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>46430</v>
+        <v>46409</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>7.4,D15</t>
+          <t>7.1,7.2</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Transaction ledger</t>
-        </is>
-      </c>
-      <c r="AA63" s="23" t="n"/>
-      <c r="AB63" s="23" t="n"/>
-      <c r="AC63" s="23" t="n"/>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="Z63" s="11" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>F10 — Web app for organisers &amp; partners: events, tournaments, scoring, service &amp; booking management</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Srivin</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>46415</v>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>46430</v>
-      </c>
-      <c r="G64" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>Web application</t>
-        </is>
-      </c>
-      <c r="AA64" s="21" t="n"/>
-      <c r="AB64" s="21" t="n"/>
-      <c r="AC64" s="21" t="n"/>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>R4 LIVE — F7, F8</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v>46414</v>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>46414</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="AA64" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Hardening: reconciliation check vs gateway, UAT; store submission</t>
+          <t>Hypercare + KT checklist sign-off (R4)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -3693,21 +3693,21 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Joint</t>
+          <t>Srivin</t>
         </is>
       </c>
       <c r="E65" s="10" t="n">
-        <v>46433</v>
+        <v>46414</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>46437</v>
+        <v>46420</v>
       </c>
       <c r="G65" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>8.1,8.2</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
@@ -3715,63 +3715,57 @@
           <t>Release, KT &amp; warranty</t>
         </is>
       </c>
-      <c r="AD65" s="11" t="n"/>
+      <c r="AA65" s="11" t="n"/>
+      <c r="AB65" s="11" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>R5 LIVE — F9, F10</t>
-        </is>
-      </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v>46441</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>46441</v>
-      </c>
-      <c r="G66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="12" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="I66" s="12" t="inlineStr">
-        <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="AE66" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Release R5 — F9 Transaction Ledger, F10 Web App (Organisers &amp; Partners) (23 Feb 2027)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="6" t="n">
+        <v>46415</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>46448</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Transaction ledger</t>
+        </is>
+      </c>
+      <c r="AA66" s="7" t="n"/>
+      <c r="AB66" s="7" t="n"/>
+      <c r="AC66" s="7" t="n"/>
+      <c r="AD66" s="7" t="n"/>
+      <c r="AE66" s="7" t="n"/>
+      <c r="AF66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Hypercare + KT checklist sign-off (R5)</t>
+          <t>F9 — Transaction Ledger: webhook ingestion + reconciliation, admin history/detail, PDF/CSV export, refund tracker</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -3785,76 +3779,81 @@
         </is>
       </c>
       <c r="E67" s="10" t="n">
-        <v>46441</v>
+        <v>46415</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>46448</v>
+        <v>46430</v>
       </c>
       <c r="G67" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.4,D15</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="AE67" s="11" t="n"/>
-      <c r="AF67" s="11" t="n"/>
+          <t>Transaction ledger</t>
+        </is>
+      </c>
+      <c r="AA67" s="23" t="n"/>
+      <c r="AB67" s="23" t="n"/>
+      <c r="AC67" s="23" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>Release R6 — F11 Split Settlement &amp; Partner Payouts, F12 WhatsApp &amp; Full Alert Catalog (23 Mar 2027)</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="6" t="n">
-        <v>46442</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>46486</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="AE68" s="7" t="n"/>
-      <c r="AF68" s="7" t="n"/>
-      <c r="AG68" s="7" t="n"/>
-      <c r="AH68" s="7" t="n"/>
-      <c r="AI68" s="7" t="n"/>
-      <c r="AJ68" s="7" t="n"/>
-      <c r="AK68" s="7" t="n"/>
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>F10 — Web app for organisers &amp; partners: events, tournaments, scoring, service &amp; booking management</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>46415</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>46430</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>Web application</t>
+        </is>
+      </c>
+      <c r="AA68" s="21" t="n"/>
+      <c r="AB68" s="21" t="n"/>
+      <c r="AC68" s="21" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>F11 — Razorpay Route onboarding for all partner types + partner settlement view (web)</t>
+          <t>Hardening: reconciliation check vs gateway, UAT; store submission</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -3864,85 +3863,85 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E69" s="10" t="n">
-        <v>46442</v>
+        <v>46433</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>46458</v>
+        <v>46437</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>8.4,D10</t>
+          <t>8.1,8.2</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>Partner &amp; service</t>
-        </is>
-      </c>
-      <c r="AE69" s="22" t="n"/>
-      <c r="AF69" s="22" t="n"/>
-      <c r="AG69" s="22" t="n"/>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="AD69" s="11" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>F12 — WhatsApp channel + full SOW Section 10.2 alert catalog</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Srivin</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>46442</v>
-      </c>
-      <c r="F70" s="10" t="n">
-        <v>46458</v>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>8.4,D13</t>
-        </is>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="AE70" s="19" t="n"/>
-      <c r="AF70" s="19" t="n"/>
-      <c r="AG70" s="19" t="n"/>
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>R5 LIVE — F9, F10</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Joint</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v>46441</v>
+      </c>
+      <c r="F70" s="14" t="n">
+        <v>46441</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="AE70" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Enabler — offline import tools for completed-event data</t>
+          <t>Hypercare + KT checklist sign-off (R5)</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -3956,124 +3955,120 @@
         </is>
       </c>
       <c r="E71" s="10" t="n">
+        <v>46441</v>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>46448</v>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="AE71" s="11" t="n"/>
+      <c r="AF71" s="11" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Release R6 — F11 Split Settlement &amp; Partner Payouts, F12 WhatsApp &amp; Full Alert Catalog (23 Mar 2027)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="6" t="n">
         <v>46442</v>
       </c>
-      <c r="F71" s="10" t="n">
-        <v>46451</v>
-      </c>
-      <c r="G71" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>8.4,D19</t>
-        </is>
-      </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>Booking &amp; events</t>
-        </is>
-      </c>
-      <c r="AE71" s="20" t="n"/>
-      <c r="AF71" s="20" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Hardening: full end-to-end regression, performance test, full VAPT (pre-completion), UAT</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="F72" s="6" t="n">
+        <v>46486</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="AE72" s="7" t="n"/>
+      <c r="AF72" s="7" t="n"/>
+      <c r="AG72" s="7" t="n"/>
+      <c r="AH72" s="7" t="n"/>
+      <c r="AI72" s="7" t="n"/>
+      <c r="AJ72" s="7" t="n"/>
+      <c r="AK72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>F11 — Razorpay Route onboarding for all partner types + partner settlement view (web)</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="F72" s="10" t="n">
-        <v>46465</v>
-      </c>
-      <c r="G72" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>9.1,9.2,9.3</t>
-        </is>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="AH72" s="11" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>R6 LIVE — F11, F12 — PHASE 2A COMPLETE</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="E73" s="14" t="n">
-        <v>46469</v>
-      </c>
-      <c r="F73" s="14" t="n">
-        <v>46469</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="12" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="AI73" s="15" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>46442</v>
+      </c>
+      <c r="F73" s="10" t="n">
+        <v>46458</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>8.4,D10</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>Partner &amp; service</t>
+        </is>
+      </c>
+      <c r="AE73" s="22" t="n"/>
+      <c r="AF73" s="22" t="n"/>
+      <c r="AG73" s="22" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Hypercare</t>
+          <t>F12 — WhatsApp channel + full SOW Section 10.2 alert catalog</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -4087,36 +4082,37 @@
         </is>
       </c>
       <c r="E74" s="10" t="n">
-        <v>46469</v>
+        <v>46442</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>46479</v>
+        <v>46458</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.4,D13</t>
         </is>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="AI74" s="11" t="n"/>
-      <c r="AJ74" s="11" t="n"/>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="AE74" s="19" t="n"/>
+      <c r="AF74" s="19" t="n"/>
+      <c r="AG74" s="19" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Infrastructure operations runbook &amp; transition plan (SOW 15.1)</t>
+          <t>Enabler — offline import tools for completed-event data</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -4130,37 +4126,36 @@
         </is>
       </c>
       <c r="E75" s="10" t="n">
-        <v>46454</v>
+        <v>46442</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>46472</v>
+        <v>46451</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>9.1SS</t>
+          <t>8.4,D19</t>
         </is>
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>Release, KT &amp; warranty</t>
-        </is>
-      </c>
-      <c r="AG75" s="11" t="n"/>
-      <c r="AH75" s="11" t="n"/>
-      <c r="AI75" s="11" t="n"/>
+          <t>Booking &amp; events</t>
+        </is>
+      </c>
+      <c r="AE75" s="20" t="n"/>
+      <c r="AF75" s="20" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Final KT: platform operations and architecture walkthrough</t>
+          <t>Hardening: full end-to-end regression, performance test, full VAPT (pre-completion), UAT</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -4170,21 +4165,21 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Srivin</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E76" s="10" t="n">
-        <v>46470</v>
+        <v>46461</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>46479</v>
+        <v>46465</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.1,9.2,9.3</t>
         </is>
       </c>
       <c r="I76" s="8" t="inlineStr">
@@ -4192,18 +4187,17 @@
           <t>Release, KT &amp; warranty</t>
         </is>
       </c>
-      <c r="AI76" s="11" t="n"/>
-      <c r="AJ76" s="11" t="n"/>
+      <c r="AH76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>Phase 2A acceptance &amp; KT checklist sign-off</t>
+          <t>R6 LIVE — F11, F12 — PHASE 2A COMPLETE</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -4213,21 +4207,21 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>SportSeek</t>
+          <t>Joint</t>
         </is>
       </c>
       <c r="E77" s="14" t="n">
-        <v>46479</v>
+        <v>46469</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>46479</v>
+        <v>46469</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>9.7,9.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
@@ -4235,90 +4229,64 @@
           <t>Release, KT &amp; warranty</t>
         </is>
       </c>
-      <c r="AJ77" s="15" t="inlineStr">
+      <c r="AI77" s="15" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>Continuous Support Obligations</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr"/>
-      <c r="E78" s="6" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>46559</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>175</v>
-      </c>
-      <c r="H78" s="4" t="inlineStr"/>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Hypercare</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>46469</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>46479</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>Release, KT &amp; warranty</t>
         </is>
       </c>
-      <c r="M78" s="7" t="n"/>
-      <c r="N78" s="7" t="n"/>
-      <c r="O78" s="7" t="n"/>
-      <c r="P78" s="7" t="n"/>
-      <c r="Q78" s="7" t="n"/>
-      <c r="R78" s="7" t="n"/>
-      <c r="S78" s="7" t="n"/>
-      <c r="T78" s="7" t="n"/>
-      <c r="U78" s="7" t="n"/>
-      <c r="V78" s="7" t="n"/>
-      <c r="W78" s="7" t="n"/>
-      <c r="X78" s="7" t="n"/>
-      <c r="Y78" s="7" t="n"/>
-      <c r="Z78" s="7" t="n"/>
-      <c r="AA78" s="7" t="n"/>
-      <c r="AB78" s="7" t="n"/>
-      <c r="AC78" s="7" t="n"/>
-      <c r="AD78" s="7" t="n"/>
-      <c r="AE78" s="7" t="n"/>
-      <c r="AF78" s="7" t="n"/>
-      <c r="AG78" s="7" t="n"/>
-      <c r="AH78" s="7" t="n"/>
-      <c r="AI78" s="7" t="n"/>
-      <c r="AJ78" s="7" t="n"/>
-      <c r="AK78" s="7" t="n"/>
-      <c r="AL78" s="7" t="n"/>
-      <c r="AM78" s="7" t="n"/>
-      <c r="AN78" s="7" t="n"/>
-      <c r="AO78" s="7" t="n"/>
-      <c r="AP78" s="7" t="n"/>
-      <c r="AQ78" s="7" t="n"/>
-      <c r="AR78" s="7" t="n"/>
-      <c r="AS78" s="7" t="n"/>
-      <c r="AT78" s="7" t="n"/>
-      <c r="AU78" s="7" t="n"/>
-      <c r="AV78" s="7" t="n"/>
+      <c r="AI78" s="11" t="n"/>
+      <c r="AJ78" s="11" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Phase 1 production monitoring &amp; bug fixes (SOW Section 16)</t>
+          <t>Infrastructure operations runbook &amp; transition plan (SOW 15.1)</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -4332,17 +4300,17 @@
         </is>
       </c>
       <c r="E79" s="10" t="n">
-        <v>46315</v>
+        <v>46454</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>46486</v>
+        <v>46472</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>9.1SS</t>
         </is>
       </c>
       <c r="I79" s="8" t="inlineStr">
@@ -4350,41 +4318,19 @@
           <t>Release, KT &amp; warranty</t>
         </is>
       </c>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n"/>
-      <c r="O79" s="11" t="n"/>
-      <c r="P79" s="11" t="n"/>
-      <c r="Q79" s="11" t="n"/>
-      <c r="R79" s="11" t="n"/>
-      <c r="S79" s="11" t="n"/>
-      <c r="T79" s="11" t="n"/>
-      <c r="U79" s="11" t="n"/>
-      <c r="V79" s="11" t="n"/>
-      <c r="W79" s="11" t="n"/>
-      <c r="X79" s="11" t="n"/>
-      <c r="Y79" s="11" t="n"/>
-      <c r="Z79" s="11" t="n"/>
-      <c r="AA79" s="11" t="n"/>
-      <c r="AB79" s="11" t="n"/>
-      <c r="AC79" s="11" t="n"/>
-      <c r="AD79" s="11" t="n"/>
-      <c r="AE79" s="11" t="n"/>
-      <c r="AF79" s="11" t="n"/>
       <c r="AG79" s="11" t="n"/>
       <c r="AH79" s="11" t="n"/>
       <c r="AI79" s="11" t="n"/>
-      <c r="AJ79" s="11" t="n"/>
-      <c r="AK79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>90-day warranty per release (R1 → 18 Jan 2027 … R6 → 21 Jun 2027)</t>
+          <t>Final KT: platform operations and architecture walkthrough</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -4398,17 +4344,17 @@
         </is>
       </c>
       <c r="E80" s="10" t="n">
-        <v>46315</v>
+        <v>46470</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>46559</v>
+        <v>46479</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr">
@@ -4416,45 +4362,269 @@
           <t>Release, KT &amp; warranty</t>
         </is>
       </c>
-      <c r="M80" s="11" t="n"/>
-      <c r="N80" s="11" t="n"/>
-      <c r="O80" s="11" t="n"/>
-      <c r="P80" s="11" t="n"/>
-      <c r="Q80" s="11" t="n"/>
-      <c r="R80" s="11" t="n"/>
-      <c r="S80" s="11" t="n"/>
-      <c r="T80" s="11" t="n"/>
-      <c r="U80" s="11" t="n"/>
-      <c r="V80" s="11" t="n"/>
-      <c r="W80" s="11" t="n"/>
-      <c r="X80" s="11" t="n"/>
-      <c r="Y80" s="11" t="n"/>
-      <c r="Z80" s="11" t="n"/>
-      <c r="AA80" s="11" t="n"/>
-      <c r="AB80" s="11" t="n"/>
-      <c r="AC80" s="11" t="n"/>
-      <c r="AD80" s="11" t="n"/>
-      <c r="AE80" s="11" t="n"/>
-      <c r="AF80" s="11" t="n"/>
-      <c r="AG80" s="11" t="n"/>
-      <c r="AH80" s="11" t="n"/>
       <c r="AI80" s="11" t="n"/>
       <c r="AJ80" s="11" t="n"/>
-      <c r="AK80" s="11" t="n"/>
-      <c r="AL80" s="11" t="n"/>
-      <c r="AM80" s="11" t="n"/>
-      <c r="AN80" s="11" t="n"/>
-      <c r="AO80" s="11" t="n"/>
-      <c r="AP80" s="11" t="n"/>
-      <c r="AQ80" s="11" t="n"/>
-      <c r="AR80" s="11" t="n"/>
-      <c r="AS80" s="11" t="n"/>
-      <c r="AT80" s="11" t="n"/>
-      <c r="AU80" s="11" t="n"/>
-      <c r="AV80" s="11" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>Phase 2A acceptance &amp; KT checklist sign-off</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>SportSeek</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>46479</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>46479</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>9.7,9.8</t>
+        </is>
+      </c>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="AJ81" s="15" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Continuous Support Obligations</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr"/>
+      <c r="E82" s="6" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>46559</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="n"/>
+      <c r="N82" s="7" t="n"/>
+      <c r="O82" s="7" t="n"/>
+      <c r="P82" s="7" t="n"/>
+      <c r="Q82" s="7" t="n"/>
+      <c r="R82" s="7" t="n"/>
+      <c r="S82" s="7" t="n"/>
+      <c r="T82" s="7" t="n"/>
+      <c r="U82" s="7" t="n"/>
+      <c r="V82" s="7" t="n"/>
+      <c r="W82" s="7" t="n"/>
+      <c r="X82" s="7" t="n"/>
+      <c r="Y82" s="7" t="n"/>
+      <c r="Z82" s="7" t="n"/>
+      <c r="AA82" s="7" t="n"/>
+      <c r="AB82" s="7" t="n"/>
+      <c r="AC82" s="7" t="n"/>
+      <c r="AD82" s="7" t="n"/>
+      <c r="AE82" s="7" t="n"/>
+      <c r="AF82" s="7" t="n"/>
+      <c r="AG82" s="7" t="n"/>
+      <c r="AH82" s="7" t="n"/>
+      <c r="AI82" s="7" t="n"/>
+      <c r="AJ82" s="7" t="n"/>
+      <c r="AK82" s="7" t="n"/>
+      <c r="AL82" s="7" t="n"/>
+      <c r="AM82" s="7" t="n"/>
+      <c r="AN82" s="7" t="n"/>
+      <c r="AO82" s="7" t="n"/>
+      <c r="AP82" s="7" t="n"/>
+      <c r="AQ82" s="7" t="n"/>
+      <c r="AR82" s="7" t="n"/>
+      <c r="AS82" s="7" t="n"/>
+      <c r="AT82" s="7" t="n"/>
+      <c r="AU82" s="7" t="n"/>
+      <c r="AV82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>Phase 1 production monitoring &amp; bug fixes (SOW Section 16)</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>46486</v>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="n"/>
+      <c r="N83" s="11" t="n"/>
+      <c r="O83" s="11" t="n"/>
+      <c r="P83" s="11" t="n"/>
+      <c r="Q83" s="11" t="n"/>
+      <c r="R83" s="11" t="n"/>
+      <c r="S83" s="11" t="n"/>
+      <c r="T83" s="11" t="n"/>
+      <c r="U83" s="11" t="n"/>
+      <c r="V83" s="11" t="n"/>
+      <c r="W83" s="11" t="n"/>
+      <c r="X83" s="11" t="n"/>
+      <c r="Y83" s="11" t="n"/>
+      <c r="Z83" s="11" t="n"/>
+      <c r="AA83" s="11" t="n"/>
+      <c r="AB83" s="11" t="n"/>
+      <c r="AC83" s="11" t="n"/>
+      <c r="AD83" s="11" t="n"/>
+      <c r="AE83" s="11" t="n"/>
+      <c r="AF83" s="11" t="n"/>
+      <c r="AG83" s="11" t="n"/>
+      <c r="AH83" s="11" t="n"/>
+      <c r="AI83" s="11" t="n"/>
+      <c r="AJ83" s="11" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>90-day warranty per release (R1 → 18 Jan 2027 … R6 → 21 Jun 2027)</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Srivin</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>46559</v>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>Release, KT &amp; warranty</t>
+        </is>
+      </c>
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="11" t="n"/>
+      <c r="O84" s="11" t="n"/>
+      <c r="P84" s="11" t="n"/>
+      <c r="Q84" s="11" t="n"/>
+      <c r="R84" s="11" t="n"/>
+      <c r="S84" s="11" t="n"/>
+      <c r="T84" s="11" t="n"/>
+      <c r="U84" s="11" t="n"/>
+      <c r="V84" s="11" t="n"/>
+      <c r="W84" s="11" t="n"/>
+      <c r="X84" s="11" t="n"/>
+      <c r="Y84" s="11" t="n"/>
+      <c r="Z84" s="11" t="n"/>
+      <c r="AA84" s="11" t="n"/>
+      <c r="AB84" s="11" t="n"/>
+      <c r="AC84" s="11" t="n"/>
+      <c r="AD84" s="11" t="n"/>
+      <c r="AE84" s="11" t="n"/>
+      <c r="AF84" s="11" t="n"/>
+      <c r="AG84" s="11" t="n"/>
+      <c r="AH84" s="11" t="n"/>
+      <c r="AI84" s="11" t="n"/>
+      <c r="AJ84" s="11" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+      <c r="AL84" s="11" t="n"/>
+      <c r="AM84" s="11" t="n"/>
+      <c r="AN84" s="11" t="n"/>
+      <c r="AO84" s="11" t="n"/>
+      <c r="AP84" s="11" t="n"/>
+      <c r="AQ84" s="11" t="n"/>
+      <c r="AR84" s="11" t="n"/>
+      <c r="AS84" s="11" t="n"/>
+      <c r="AT84" s="11" t="n"/>
+      <c r="AU84" s="11" t="n"/>
+      <c r="AV84" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I80"/>
+  <autoFilter ref="A3:I84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4465,7 +4635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4631,12 +4801,12 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Launch scope and go-live criteria sign-off</t>
+          <t>Identity decisions for F3: which identifiers link accounts (phone, email), role list, KYC fields to carry, user messaging for linking</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -4645,16 +4815,16 @@
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Freeze date at risk</t>
+          <t>F3 cannot be built for R1; launches with Phase 1 login and F3 follows in R2</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -4667,12 +4837,12 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Expected launch peak concurrent users (load-test target)</t>
+          <t>Launch scope and go-live criteria sign-off</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4681,16 +4851,16 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Load test runs against an assumed figure</t>
+          <t>Freeze date at risk</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -4703,12 +4873,12 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Legal content: privacy policy, terms, DPDP notice text, store listing copy &amp; assets</t>
+          <t>Expected launch peak concurrent users (load-test target)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4717,16 +4887,16 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>2.8, 2.12</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Store submission blocked</t>
+          <t>Load test runs against an assumed figure</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -4739,12 +4909,12 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Apple App Store &amp; Google Play developer accounts (SportSeek-owned) with release rights</t>
+          <t>Legal content: privacy policy, terms, DPDP notice text (covering shared identity), store listing copy &amp; assets</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4753,11 +4923,11 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>46294</v>
+        <v>46304</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13, 2.15</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -4775,12 +4945,12 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Requirement tool decision (JIRA or Trello) and workspace</t>
+          <t>Apple App Store &amp; Google Play developer accounts (SportSeek-owned) with release rights</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4789,16 +4959,16 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Backlog managed off-tool temporarily</t>
+          <t>Store submission blocked</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -4811,12 +4981,12 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Names of SportSeek developers joining the pod (2 recommended)</t>
+          <t>Requirement tool decision (JIRA or Trello) and workspace</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4825,16 +4995,16 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>46318</v>
+        <v>46297</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>R2 onward</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Capacity plan re-baselined</t>
+          <t>Backlog managed off-tool temporarily</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -4847,30 +5017,30 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Written confirmation that Razorpay Route (split settlement) is enabled for coach, physio and nutritionist partner categories</t>
+          <t>Names of SportSeek developers joining the pod (2 recommended)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>SportSeek / Razorpay</t>
+          <t>SportSeek</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>46332</v>
+        <v>46318</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>R2 onward</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>F11 moves to a later train; SOW 8.3 compliance design unconfirmed</t>
+          <t>Capacity plan re-baselined</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -4883,30 +5053,30 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Refund &amp; cancellation business policy (approver, timeframes, non-refundable items)</t>
+          <t>Written confirmation that Razorpay Route (split settlement) is enabled for coach, physio and nutritionist partner categories</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>SportSeek</t>
+          <t>SportSeek / Razorpay</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>F5 moves to a later train</t>
+          <t>F11 moves to a later train; SOW 8.3 compliance design unconfirmed</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -4919,12 +5089,12 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Email/SMS templates for F1–F2 (SMS templates registered on DLT); full alert catalog and templates by 8 Jan 2027</t>
+          <t>Refund &amp; cancellation business policy (approver, timeframes, non-refundable items)</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -4933,16 +5103,16 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>46300</v>
+        <v>46339</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>2.9, 2.10, 9.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>F2 SMS reminders ship as email-only; F12 slips</t>
+          <t>F5 moves to a later train</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -4955,12 +5125,12 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp Business Solution Provider contract; Meta-approved message templates</t>
+          <t>Email/SMS templates for F1–F2 (SMS templates registered on DLT); full alert catalog and templates by 8 Jan 2027</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -4969,16 +5139,16 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>46423</v>
+        <v>46325</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>5.1, 5.2, 9.2</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>WhatsApp part of F12 slips to next train</t>
+          <t>F2 SMS reminders ship as email/push only; F12 slips</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -4991,12 +5161,12 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Email provider account (by 5 Oct) and FCM/APNs credentials (by 30 Oct) in SportSeek accounts</t>
+          <t>WhatsApp Business Solution Provider contract; Meta-approved message templates</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5005,16 +5175,16 @@
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>46300</v>
+        <v>46423</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>2.9, 5.2</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>F1 or F4 slips</t>
+          <t>WhatsApp part of F12 slips to next train</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -5027,12 +5197,12 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Decision: Transaction Ledger in Admin + partner web only, or also in User/Partner apps (SOW 8.1 open item)</t>
+          <t>Email provider account and FCM/APNs credentials in SportSeek accounts</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5041,16 +5211,16 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>46395</v>
+        <v>46321</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.1, 5.3</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Ledger scope unconfirmed</t>
+          <t>F1 or F4 slips</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -5063,12 +5233,12 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Warranty SLA numbers (acknowledge/resolve times) — SOW Section 16 open item</t>
+          <t>Decision: Transaction Ledger in Admin + partner web only, or also in User/Partner apps (SOW 8.1 open item)</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5077,16 +5247,16 @@
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>46325</v>
+        <v>46395</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Support model</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Default proposal applies</t>
+          <t>Ledger scope unconfirmed</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -5099,12 +5269,12 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>UI/UX approvals turned around within 2 working days of submission</t>
+          <t>Warranty SLA numbers (acknowledge/resolve times) — SOW Section 16 open item</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5112,19 +5282,17 @@
           <t>SportSeek</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+      <c r="D18" s="25" t="n">
+        <v>46325</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>3.6, 3.7</t>
+          <t>Support model</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Feature rides the next train</t>
+          <t>Default proposal applies</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -5137,12 +5305,12 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D17</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Approval of account-merge rules for existing duplicate identities</t>
+          <t>UI/UX approvals turned around within 2 working days of submission</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5150,17 +5318,19 @@
           <t>SportSeek</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
-        <v>46346</v>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>3.6, 3.7</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Identity migration moves to R4</t>
+          <t>Feature rides the next train</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -5173,12 +5343,12 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Historical completed-event data files for import</t>
+          <t>Approval of account-merge rules for existing duplicate identities</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5187,16 +5357,16 @@
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>46437</v>
+        <v>46325</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Import tool tested with synthetic data only</t>
+          <t>Duplicate merge moves to R3; linking still works for new registrations</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -5209,12 +5379,12 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Phase 2A NFR targets: API p95 latency, peak concurrency, uptime SLA</t>
+          <t>Historical completed-event data files for import</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5223,16 +5393,16 @@
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>46325</v>
+        <v>46437</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>3.3, all hardening</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Performance acceptance undefined</t>
+          <t>Import tool tested with synthetic data only</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -5245,38 +5415,74 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2A NFR targets: API p95 latency, peak concurrency, uptime SLA</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>SportSeek</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>46325</v>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>3.3, all hardening</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Performance acceptance undefined</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
           <t>D21</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Approval of Srivin's AI tooling on SportSeek code (enterprise terms, no training on client data, data-handling rules)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>SportSeek</t>
         </is>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D23" s="25" t="n">
         <v>46294</v>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Delivery falls back to conventional pace and team size</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr"/>
+      <c r="H23" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5359,7 +5565,7 @@
       </c>
       <c r="B3" s="26" t="inlineStr">
         <is>
-          <t>Launch Scope Gate: launch scope, go-live criteria, F1/F2 confirmed</t>
+          <t>Launch Scope Gate: launch scope, go-live criteria, F3 scope and fallback confirmed</t>
         </is>
       </c>
       <c r="C3" s="26" t="inlineStr">
@@ -5379,12 +5585,12 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="B4" s="26" t="inlineStr">
         <is>
-          <t>Code freeze &amp; Release Candidate</t>
+          <t>Code freeze &amp; Release Candidate (F3 behind flag)</t>
         </is>
       </c>
       <c r="C4" s="26" t="inlineStr">
@@ -5397,19 +5603,19 @@
       </c>
       <c r="E4" s="26" t="inlineStr">
         <is>
-          <t>2.5,2.9,2.10</t>
+          <t>2.5,2.7,2.8,2.9,2.10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>Go / No-Go</t>
+          <t>Go / No-Go (separate decision: F3 on or off at launch)</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
@@ -5422,19 +5628,19 @@
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2.12,2.13,2.14</t>
+          <t>2.15,2.16,2.17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
-          <t>R1 LIVE — public launch with F1 and F2</t>
+          <t>R1 LIVE — public launch with F3 Shared Identity</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">
@@ -5447,7 +5653,7 @@
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.18</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5735,12 @@
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>R2 LIVE — F3, F4</t>
+          <t>R2 LIVE — F1, F2, F4; duplicate accounts merged</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
@@ -5547,14 +5753,14 @@
       </c>
       <c r="E10" s="26" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
@@ -5572,7 +5778,7 @@
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6251,7 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>2</v>
@@ -6066,7 +6272,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
@@ -6146,8 +6352,8 @@
           <t>Senior (7+ yrs)</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n">
-        <v>1</v>
+      <c r="D8" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>1</v>
@@ -6168,7 +6374,7 @@
         <v>0.25</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
@@ -6351,7 +6557,7 @@
         </is>
       </c>
       <c r="D12" s="31" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E12" s="31" t="n">
         <v>0.25</v>
@@ -6372,11 +6578,11 @@
         <v>0</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Web, API and mobile penetration testing (OWASP WSTG, MASTG); targeted pen tests on identity (R2), refunds (R3) and payouts (R6); full VAPT before Phase 2A completion</t>
+          <t>Web, API and mobile penetration testing (OWASP WSTG, MASTG); targeted pen tests on identity (R1), refunds (R3) and payouts (R6); full VAPT before Phase 2A completion</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
